--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>E.g. Patient, Practitioner, RelatedPerson, Organization, Location, Device</t>
@@ -669,7 +669,7 @@
     <t>The possible types of subjects for a measure (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Measure.date</t>
@@ -798,7 +798,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -943,7 +943,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Measure.author</t>
@@ -1010,7 +1010,7 @@
     <t>Measure.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.0.1)
 </t>
   </si>
   <si>
@@ -1047,7 +1047,7 @@
     <t>The scoring type of the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-scoring</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-scoring|4.0.1</t>
   </si>
   <si>
     <t>Measure.compositeScoring</t>
@@ -1062,7 +1062,7 @@
     <t>The composite scoring method of the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/composite-measure-scoring</t>
+    <t>http://hl7.org/fhir/ValueSet/composite-measure-scoring|4.0.1</t>
   </si>
   <si>
     <t>Measure.type</t>
@@ -1077,7 +1077,7 @@
     <t>The type of measure (includes codes from 2.16.840.1.113883.1.11.20368).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-type</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-type|4.0.1</t>
   </si>
   <si>
     <t>Measure.riskAdjustment</t>
@@ -1266,7 +1266,7 @@
     <t>The type of population.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-population</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-population|4.0.1</t>
   </si>
   <si>
     <t>Measure.group.population.description</t>
@@ -1433,7 +1433,7 @@
     <t>The intended usage for supplemental data elements in the measure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/measure-data-usage</t>
+    <t>http://hl7.org/fhir/ValueSet/measure-data-usage|4.0.1</t>
   </si>
   <si>
     <t>Measure.supplementalData.description</t>
@@ -1769,17 +1769,17 @@
   <dimension ref="A1:AN84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.046875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="19.62890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1788,26 +1788,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="139.44140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.8515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="119.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.5390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="48.05859375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="143.74609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3072,7 +3072,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>185</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>210</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>253</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>290</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>337</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>387</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>390</v>
       </c>
@@ -11408,12 +11408,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN84">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-measure.xlsx
+++ b/main/ig/StructureDefinition-ror-measure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
